--- a/question1/efficiency/results/result1.xlsx
+++ b/question1/efficiency/results/result1.xlsx
@@ -17,14 +17,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,8 +52,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B147"/>
+  <dimension ref="A1:B145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -422,1475 +431,1455 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>购电量(kWh)</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>时间段</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>购电量</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:10</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1406.6411</v>
+          <t>0:10-0:20</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1406.3299</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:20</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1406.329867</v>
+          <t>0:20-0:30</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1407.3838</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1407.38385</v>
+          <t>0:30-0:40</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1409.0739</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:40</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1409.07395</v>
+          <t>0:40-0:50</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1409.8045</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:50</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1409.80455</v>
+          <t>0:50-1:00</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>576.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>576.6400169999999</v>
+          <t>1:00-1:10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>577.8597</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:10</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>577.8597</v>
+          <t>1:10-1:20</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>577.9939000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:20</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>577.993867</v>
+          <t>1:20-1:30</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>637.4723</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>637.472306</v>
+          <t>1:30-1:40</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>580.4154</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:40</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>580.41545</v>
+          <t>1:40-1:50</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>582.514</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:50</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>582.514017</v>
+          <t>1:50-2:00</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>583.074</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>583.0740500000001</v>
+          <t>2:00-2:10</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>584.2049</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>584.204917</v>
+          <t>2:10-2:20</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>585.4398</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:20</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>585.439783</v>
+          <t>2:20-2:30</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>586.1446999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>586.14475</v>
+          <t>2:30-2:40</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>586.3208</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:40</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>586.320767</v>
+          <t>2:40-2:50</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>586.4253</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:50</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>586.4253</v>
+          <t>2:50-3:00</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>586.8496</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>586.8496</v>
+          <t>3:00-3:10</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>587.821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>03:10</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>587.821017</v>
+          <t>3:10-3:20</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>589.5476</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>03:20</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>589.547567</v>
+          <t>3:20-3:30</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>590.8135</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>590.8134669999999</v>
+          <t>3:30-3:40</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>590.2131000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>03:40</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>590.213117</v>
+          <t>3:40-3:50</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>591.0663</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>03:50</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>591.066267</v>
+          <t>3:50-4:00</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>593.3678</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>593.367833</v>
+          <t>4:00-4:10</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>593.6597</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>04:10</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>593.659683</v>
+          <t>4:10-4:20</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>592.7864</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>04:20</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>592.786383</v>
+          <t>4:20-4:30</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>593.3379</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>593.337867</v>
+          <t>4:30-4:40</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>596.6758</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>04:40</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>596.675767</v>
+          <t>4:40-4:50</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>597.7803</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>04:50</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>597.78025</v>
+          <t>4:50-5:00</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>595.1625</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>595.1625</v>
+          <t>5:00-5:10</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>590.6065</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:10</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>590.6065</v>
+          <t>5:10-5:20</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>589.4852</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:20</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>589.485183</v>
+          <t>5:20-5:30</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>578.4554000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>578.45545</v>
+          <t>5:30-5:40</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>1383.6598</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:40</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1383.659783</v>
+          <t>5:40-5:50</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:50</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
+          <t>5:50-6:00</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
+          <t>6:00-6:10</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:10</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
+          <t>6:10-6:20</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
+          <t>6:20-6:30</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
+          <t>6:30-6:40</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
+          <t>6:40-6:50</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
+          <t>6:50-7:00</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
+          <t>7:00-7:10</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
+          <t>7:10-7:20</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
+          <t>7:20-7:30</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
+          <t>7:30-7:40</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:40</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
+          <t>7:40-7:50</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:50</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
+          <t>7:50-8:00</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
+          <t>8:00-8:10</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:10</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
+          <t>8:10-8:20</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
+          <t>8:20-8:30</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
+          <t>8:30-8:40</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
+          <t>8:40-8:50</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
+          <t>8:50-9:00</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
+          <t>9:00-9:10</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
+          <t>9:10-9:20</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
+          <t>9:20-9:30</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
+          <t>9:30-9:40</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
+          <t>9:40-9:50</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
+          <t>9:50-10:00</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
+          <t>10:00-10:10</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
+          <t>10:10-10:20</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
+          <t>10:20-10:30</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
+          <t>10:30-10:40</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
+          <t>10:40-10:50</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
+          <t>10:50-11:00</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0</v>
+          <t>11:00-11:10</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>415.1177</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>415.11767</v>
+          <t>11:10-11:20</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
+          <t>11:20-11:30</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
+          <t>11:30-11:40</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0</v>
+          <t>11:40-11:50</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>520.1245</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>520.124517</v>
+          <t>11:50-12:00</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>486.4029</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>486.4029</v>
+          <t>12:00-12:10</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>480.4124</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>480.41245</v>
+          <t>12:10-12:20</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>485.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>485.3</v>
+          <t>12:20-12:30</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>488.607</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>488.606967</v>
+          <t>12:30-12:40</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>498.2707</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>498.270733</v>
+          <t>12:40-12:50</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
+          <t>12:50-13:00</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
+          <t>13:00-13:10</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
+          <t>13:10-13:20</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
+          <t>13:20-13:30</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
+          <t>13:30-13:40</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
+          <t>13:40-13:50</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
+          <t>13:50-14:00</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
+          <t>14:00-14:10</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
+          <t>14:10-14:20</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
+          <t>14:20-14:30</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
+          <t>14:30-14:40</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
+          <t>14:40-14:50</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
+          <t>14:50-15:00</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>112.0899</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>112.089867</v>
+          <t>15:00-15:10</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>255.4856</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>255.485609</v>
+          <t>15:10-15:20</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>197.5235</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>197.523517</v>
+          <t>15:20-15:30</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>244.814</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>244.814033</v>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>295.5346</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>295.534617</v>
+          <t>15:40-15:50</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>345.7775</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>345.7775</v>
+          <t>15:50-16:00</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>394.9315</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>394.931483</v>
+          <t>16:00-16:10</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>445.4317</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>445.43165</v>
+          <t>16:10-16:20</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>495.6966</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>495.696583</v>
+          <t>16:20-16:30</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>547.1191</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>547.11905</v>
+          <t>16:30-16:40</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>599.9854</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>599.9854329999999</v>
+          <t>16:40-16:50</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>635.4297</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>635.42975</v>
+          <t>16:50-17:00</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>660.8307</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>660.830683</v>
+          <t>17:00-17:10</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>702.0368999999999</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>17:10</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>702.036933</v>
+          <t>17:10-17:20</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>738.0658</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>17:20</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>738.065783</v>
+          <t>17:20-17:30</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>775.9447</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>775.944717</v>
+          <t>17:30-17:40</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>826.0833</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>826.08325</v>
+          <t>17:40-17:50</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>762.4228000000001</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>762.4228000000001</v>
+          <t>17:50-18:00</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>636.9826</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>636.982617</v>
+          <t>18:00-18:10</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>64.53440000000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>64.534389</v>
+          <t>18:10-18:20</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>678.8305</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>678.8305329999999</v>
+          <t>18:20-18:30</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>686.2685</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>686.2685</v>
+          <t>18:30-18:40</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>696.5044</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>696.504383</v>
+          <t>18:40-18:50</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
+          <t>18:50-19:00</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
+          <t>19:00-19:10</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
+          <t>19:10-19:20</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>19:20</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
+          <t>19:20-19:30</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
+          <t>19:30-19:40</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>19:40</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
+          <t>19:40-19:50</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>19:50</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
+          <t>19:50-20:00</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
+          <t>20:00-20:10</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
+          <t>20:10-20:20</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>20:20</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
+          <t>20:20-20:30</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
+          <t>20:30-20:40</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>0</v>
+          <t>20:40-20:50</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>715.8689000000001</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>20:50</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>715.868917</v>
+          <t>20:50-21:00</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>717.0051</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>717.005117</v>
+          <t>21:00-21:10</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>720.1603</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>21:10</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>720.1603</v>
+          <t>21:10-21:20</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>717.0549</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>21:20</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>717.0548669999999</v>
+          <t>21:20-21:30</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>720.446</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>720.445967</v>
+          <t>21:30-21:40</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>738.1347</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>21:40</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>738.134717</v>
+          <t>21:40-21:50</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>671.6935999999999</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>21:50</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>671.693567</v>
+          <t>21:50-22:00</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>1393.7903</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>1393.790317</v>
+          <t>22:00-22:10</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>1384.8989</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>22:10</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>1384.8989</v>
+          <t>22:10-22:20</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>568.826</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>22:20</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>568.82605</v>
+          <t>22:20-22:30</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>1396.9886</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>1396.98855</v>
+          <t>22:30-22:40</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>1397.7599</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>22:40</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>1397.759867</v>
+          <t>22:40-22:50</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>566.7474</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>22:50</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>566.747433</v>
+          <t>22:50-23:00</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>1399.8738</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>1399.873767</v>
+          <t>23:00-23:10</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>567.8302</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>23:10</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>567.83015</v>
+          <t>23:10-23:20</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>629.0029</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>23:20</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>629.00289</v>
+          <t>23:20-23:30</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>1403.6635</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1403.663517</v>
+          <t>23:30-23:40</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>571.6154</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>23:40</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>571.615383</v>
+          <t>23:40-23:50</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>573.1768</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>23:50</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>573.176833</v>
+          <t>23:50-0:00+1</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>574.121</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>24:00</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>574.120983</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>全天购电量</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>57526.243481</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>全天购电费(元)</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>33801.495542</v>
+          <t>0:00+1-0:10+1</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>1406.6411</v>
       </c>
     </row>
   </sheetData>
@@ -1904,28 +1893,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>时间段</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>充电量(kWh)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>放电量(kWh)</t>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>充电量</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>放电量</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>时刻</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>储电量</t>
         </is>
       </c>
     </row>
@@ -1935,11 +1936,19 @@
           <t>0:00-4:00</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>4226.310923</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
+      <c r="B2" s="2" t="n">
+        <v>4226.3108</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>6000</v>
       </c>
     </row>
     <row r="3">
@@ -1948,11 +1957,19 @@
           <t>4:00-8:00</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>833.333333</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" s="2" t="n">
+        <v>833.3333</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>6956.9814</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6000</v>
       </c>
     </row>
     <row r="4">
@@ -1961,11 +1978,11 @@
           <t>8:00-12:00</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>4448.63387</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1702.996983</v>
+      <c r="B4" s="2" t="n">
+        <v>4448.6339</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1702.9969</v>
       </c>
     </row>
     <row r="5">
@@ -1974,11 +1991,11 @@
           <t>12:00-16:00</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>5274.788093</v>
-      </c>
-      <c r="C5" t="n">
-        <v>91.101383</v>
+      <c r="B5" s="2" t="n">
+        <v>5274.788</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>91.1014</v>
       </c>
     </row>
     <row r="6">
@@ -1987,11 +2004,11 @@
           <t>16:00-20:00</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>6247.491545</v>
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6247.4915</v>
       </c>
     </row>
     <row r="7">
@@ -2000,31 +2017,11 @@
           <t>20:00-24:00</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>5059.644256</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2859.868117</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>0:00储电量</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>24:00储电量</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6000</v>
+      <c r="B7" s="2" t="n">
+        <v>5059.6441</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2859.8681</v>
       </c>
     </row>
   </sheetData>
